--- a/alves-de-paiva-julien-tableau-synthèse.xlsx
+++ b/alves-de-paiva-julien-tableau-synthèse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jalves\Documents\Julien - portfolio - oral 26-27.06.2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julie\Documents\mon_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E723C5A-C9C3-4170-B884-FE157A09569F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EE2295-EF0B-4C3B-81A7-356DA042BB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -150,12 +147,6 @@
     <t>28/04/25 au 25/06/25</t>
   </si>
   <si>
-    <t>N° candidat : X</t>
-  </si>
-  <si>
-    <t>21/10/24 au 27/04/25</t>
-  </si>
-  <si>
     <t>Renouvellement d'un parc informatique à la demande d'un client dans le cadre d'un projet académique.</t>
   </si>
   <si>
@@ -169,6 +160,39 @@
   </si>
   <si>
     <t>Création d'un portofolio : résumés, explications, etc…</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel en cours de deuxième année</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>N° candidat : 2541477335</t>
+  </si>
+  <si>
+    <t>Installation d'infrastructure avec la solution Linux (client et serveur local)</t>
+  </si>
+  <si>
+    <t>21/10/24 au 30/04/26</t>
+  </si>
+  <si>
+    <t>02/09/25 au 31/08/26</t>
+  </si>
+  <si>
+    <t>Valorisation de l'image de l'organisation par projets</t>
+  </si>
+  <si>
+    <t>Installation de matériel informatique (rénovation de parc)</t>
+  </si>
+  <si>
+    <t>Gestion baie informatique : remplacement d'équipement, rebrassage.</t>
+  </si>
+  <si>
+    <t>Préparation de périphériques externes (souris, claviers, casques, etc …)</t>
+  </si>
+  <si>
+    <t>Changements de périphériques internes (disque dur, mémoire vive, nettoyage ventilateur)</t>
   </si>
 </sst>
 </file>
@@ -261,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -600,6 +624,60 @@
       <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -607,7 +685,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -615,59 +693,98 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -709,15 +826,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1044,134 +1152,134 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7265625" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.453125" customWidth="1"/>
-    <col min="44" max="16384" width="10.81640625" style="1"/>
+    <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="18.77734375" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.44140625" customWidth="1"/>
+    <col min="44" max="16384" width="10.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="34"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="29"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="36"/>
+      <c r="H3" s="42"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+    <row r="4" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="10" t="s">
+      <c r="H4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="14" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="52"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="B6" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="325.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="F7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="G7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="H7" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>18</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1209,17 +1317,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="34"/>
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1256,19 +1364,19 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1305,19 +1413,19 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>31</v>
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
-      <c r="E10" s="12"/>
+      <c r="E10" s="15"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
-      <c r="H10" s="19"/>
+      <c r="H10" s="18"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1354,19 +1462,19 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
+      <c r="B11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="15"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="19"/>
+      <c r="H11" s="18"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1403,19 +1511,19 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="19"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="18"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1452,15 +1560,19 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13"/>
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="16"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1497,17 +1609,17 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="33"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1544,19 +1656,19 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>29</v>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="C15" s="17"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="18"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="17"/>
-      <c r="H15" s="13"/>
+      <c r="H15" s="16"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1593,19 +1705,19 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
       <c r="G16" s="17"/>
-      <c r="H16" s="13"/>
+      <c r="H16" s="18"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1642,19 +1754,19 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="19"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="22"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1691,19 +1803,19 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="13"/>
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1740,19 +1852,19 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="19"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="29"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1789,15 +1901,17 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="33"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1834,11 +1948,76 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:43" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="16"/>
+    </row>
+    <row r="22" spans="1:43" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
+    </row>
+    <row r="23" spans="1:43" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="16"/>
+    </row>
+    <row r="24" spans="1:43" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
+    </row>
+    <row r="25" spans="1:43" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="16"/>
+    </row>
     <row r="26" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1881,28 +2060,40 @@
     <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9afeb195-fe8e-4d53-b966-ac86e014f9d0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b96438d6-4088-444b-a148-08e2a0c42289" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C0540109B649AC4795630F51507852BE" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b24b5783ddc2bb45fe34b7a1a06bc44d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9afeb195-fe8e-4d53-b966-ac86e014f9d0" xmlns:ns3="b96438d6-4088-444b-a148-08e2a0c42289" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="33a84ca242945553425b58f658027b0b" ns2:_="" ns3:_="">
     <xsd:import namespace="9afeb195-fe8e-4d53-b966-ac86e014f9d0"/>
@@ -2103,17 +2294,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9afeb195-fe8e-4d53-b966-ac86e014f9d0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b96438d6-4088-444b-a148-08e2a0c42289" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2124,6 +2304,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA3166D-F719-49F0-B698-E9057D9EDF6C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b96438d6-4088-444b-a148-08e2a0c42289"/>
+    <ds:schemaRef ds:uri="9afeb195-fe8e-4d53-b966-ac86e014f9d0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65237427-9C7F-4709-8B62-3B4F8F99F7A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2142,23 +2339,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA3166D-F719-49F0-B698-E9057D9EDF6C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b96438d6-4088-444b-a148-08e2a0c42289"/>
-    <ds:schemaRef ds:uri="9afeb195-fe8e-4d53-b966-ac86e014f9d0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{574C0259-CE3C-4D74-A0FE-24A73702E787}">
   <ds:schemaRefs>
